--- a/public/templates/office/EMP_DEG_020_기능정의서.xlsx
+++ b/public/templates/office/EMP_DEG_020_기능정의서.xlsx
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C12" s="170" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 SyncGuard AI 시스템 구축</t>
+          <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
         </is>
       </c>
       <c r="D12" s="121" t="n"/>
@@ -2471,13 +2471,13 @@
     <row r="22" ht="20.25" customHeight="1" s="120">
       <c r="C22" s="124" t="inlineStr">
         <is>
-          <t>그로브소프트 (EMPASY)</t>
+          <t>엠파시 (EMPASY)</t>
         </is>
       </c>
       <c r="D22" s="125" t="n"/>
       <c r="E22" s="126" t="inlineStr">
         <is>
-          <t>아모레퍼시픽</t>
+          <t>한빛글로벌</t>
         </is>
       </c>
       <c r="F22" s="127" t="n"/>
@@ -2605,17 +2605,17 @@
       </c>
       <c r="D4" s="176" t="inlineStr">
         <is>
-          <t>착수보고서(v1.8) 및 킥오프 합의(동영상 사용자 지정 장면 캡처, 티움넷/마이비커 연계, KT레몬 Option, AWS EC2) 반영</t>
+          <t>착수보고서(v1.8) 및 킥오프 합의(동영상 사용자 지정 장면 캡처, 마케팅허브/프로덕트랩 연계, KT레몬 Option, AWS EC2) 반영</t>
         </is>
       </c>
       <c r="E4" s="175" t="inlineStr">
         <is>
-          <t>그로브소프트</t>
+          <t>엠파시</t>
         </is>
       </c>
       <c r="F4" s="177" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 RA</t>
+          <t>한빛글로벌 RA</t>
         </is>
       </c>
     </row>
@@ -2987,7 +2987,7 @@
           <t>PPTX, PDF, 긴 상세페이지(JPG) 및 동영상(MP4, 최대 300MB 대외 연계 API 직접 업로드)에서 1차로 AI Agent가 OpenCV를 통해 텍스트 애니메이션 완성 시점(피크프레임)과 하단 미세 각주를 자동 추출하고, 2차로 이를 보정하기 위해 웹 화면(:3104)에서 동영상을 재생하여 사용자가 특정 화면에 멈춰 장면을 추가하거나 AI가 만든 장면을 편집·삭제합니다.
 [입력] PPTX, PDF, 긴 JPG, MP4 동영상(최대 300MB) 및 웹 화면 사용자 보정 장면
 [처리로직]
-1. 대용량 파일(300MB): 대외 연계 전용 ALB(티움넷만 오픈) 및 BO 전용 ALB(사용자대역 오픈)를 통해 S3(Intelligent-Tiering 자동 적용) 업로드
+1. 대용량 파일(300MB): 대외 연계 전용 ALB(마케팅허브만 오픈) 및 BO 전용 ALB(사용자대역 오픈)를 통해 S3(Intelligent-Tiering 자동 적용) 업로드
 2. 동영상 1차 자동 추출: AI Agent(:18083)가 OpenCV 기반으로 영상 피크프레임 및 하단 미세 각주 장면을 1차 자동 추출하여 S3에 저장
 3. 동영상 2차 웹 보정: 통합 웹 화면(:3104)에서 동영상을 재생하고 사용자가 특정 화면에 멈춰 장면을 추가하거나 AI가 생성한 장면을 편집·삭제하면, BO 서버(:18080)가 EKS Service로 AI Agent(:18083)를 호출하여 재분석 수행
 [출력] 슬라이드/피크프레임·보정 장면별 구조화 JSON 및 이미지 스냅샷 메타데이터</t>
@@ -2998,7 +2998,7 @@
           <t>PPTX, PDF, 긴 상세페이지(JPG) 및 동영상(MP4, 최대 300MB 대외 연계 API 직접 업로드)에서 1차로 AI Agent가 OpenCV를 통해 텍스트 애니메이션 완성 시점(피크프레임)과 하단 미세 각주를 자동 추출하고, 2차로 이를 보정하기 위해 웹 화면(:3104)에서 동영상을 재생하여 사용자가 특정 화면에 멈춰 장면을 추가하거나 AI가 만든 장면을 편집·삭제합니다.
 [입력] PPTX, PDF, 긴 JPG, MP4 동영상(최대 300MB) 및 웹 화면 사용자 보정 장면
 [처리로직]
-1. 대용량 파일(300MB): 대외 연계 전용 ALB(티움넷만 오픈) 및 BO 전용 ALB(사용자대역 오픈)를 통해 S3(Intelligent-Tiering 자동 적용) 업로드
+1. 대용량 파일(300MB): 대외 연계 전용 ALB(마케팅허브만 오픈) 및 BO 전용 ALB(사용자대역 오픈)를 통해 S3(Intelligent-Tiering 자동 적용) 업로드
 2. 동영상 1차 자동 추출: AI Agent(:18083)가 OpenCV 기반으로 영상 피크프레임 및 하단 미세 각주 장면을 1차 자동 추출하여 S3에 저장
 3. 동영상 2차 웹 보정: 통합 웹 화면(:3104)에서 동영상을 재생하고 사용자가 특정 화면에 멈춰 장면을 추가하거나 AI가 생성한 장면을 편집·삭제하면, BO 서버(:18080)가 EKS Service로 AI Agent(:18083)를 호출하여 재분석 수행
 [출력] 슬라이드/피크프레임·보정 장면별 구조화 JSON 및 이미지 스냅샷 메타데이터</t>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="I8" s="143" t="inlineStr">
         <is>
-          <t>식약처 화장품 표시·광고 관리 지침, 질의응답집, 서울식약청 위반 사례집 등 규제 문서를 체계적으로 적재합니다.
+          <t>식약처 제품 표시·광고 관리 지침, 질의응답집, 서울식약청 위반 사례집 등 규제 문서를 체계적으로 적재합니다.
 [입력] PDF, HWP, DOCX 형태의 식약처 및 공정위 공식 가이드라인 문서.
 [처리로직]
 1. HWP/PDF 문서 파싱 및 조항(제N조, 별표, [사례]) 단위 의미론적 청킹(Semantic Chunking).
@@ -3431,7 +3431,7 @@
 1. Dense Vector 유사도 검색 (Cosine Similarity Top-K).
 2. Sparse Keyword 검색 (BM25 / TF-IDF Top-K).
 3. RRF(Reciprocal Rank Fusion) 알고리즘으로 점수 결합 및 Re-ranking.
-4. 식약처 공식 조항, 아모레퍼시픽 과거 내부 심의 이력, 경쟁사 위반 사례 동시 검색.
+4. 식약처 공식 조항, 한빛글로벌 과거 내부 심의 이력, 경쟁사 위반 사례 동시 검색.
 [출력] 유사도 점수와 출처 메타정보가 포함된 상위 3~5개 근거 청크.</t>
         </is>
       </c>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="I20" s="143" t="inlineStr">
         <is>
-          <t>티움넷/포털 시안 및 동영상 캡처 장면 등록 시 파싱부터 집계까지 비동기 작업 파이프라인을 총괄 오케스트레이션합니다.
+          <t>마케팅허브/포털 시안 및 동영상 캡처 장면 등록 시 파싱부터 집계까지 비동기 작업 파이프라인을 총괄 오케스트레이션합니다.
 [입력] 심의요청 ID, 시안 파일 및 동영상 캡처 스냅샷 목록, 제품/처방 코드
 [처리로직]
 1. 파이프라인 단계: 시안/스냅샷 수신 ➔ 파싱·OCR(F-01/02) ➔ 문장 분리(F-03) ➔ 전성분 RDB·표현사전 룰 매칭(F-10) ➔ 법령·ProductLab 실증 RAG(F-07) ➔ 비학습 LLM 3단계 판정 및 대체문구 생성(F-11/12)
@@ -5356,10 +5356,10 @@
       </c>
       <c r="I39" s="143" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 SAML 2.0 / OIDC 기반 Single Sign-On, 최초 로그인 시 사용자 계정 자동 프로비저닝, JWT 토큰 발급.
+          <t>한빛글로벌 SAML 2.0 / OIDC 기반 Single Sign-On, 최초 로그인 시 사용자 계정 자동 프로비저닝, JWT 토큰 발급.
 [입력] 시스템 및 사용자 입력 파라미터
 [처리로직]
-아모레퍼시픽 SAML 2.0 / OIDC 기반 Single Sign-On, 최초 로그인 시 사용자 계정 자동 프로비저닝, JWT 토큰 발급.
+한빛글로벌 SAML 2.0 / OIDC 기반 Single Sign-On, 최초 로그인 시 사용자 계정 자동 프로비저닝, JWT 토큰 발급.
 [출력] 처리 결과 및 DB 반영</t>
         </is>
       </c>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="B40" s="143" t="inlineStr">
         <is>
-          <t>티움넷(MarketingHub) 양방향 API 연동</t>
+          <t>마케팅허브(MarketingHub) 양방향 API 연동</t>
         </is>
       </c>
       <c r="C40" s="142" t="inlineStr">
@@ -5424,13 +5424,13 @@
       </c>
       <c r="I40" s="143" t="inlineStr">
         <is>
-          <t>티움넷에서 광고 시안·동영상 심의 의뢰를 수신하고, AI 사전 판정 대조 뷰어 링크 제공 및 RA 최종 확정 결과를 회신합니다.
-[입력] 티움넷 심의신청 페이로드(수신), AI 판정 뷰어 딥링크 및 RA 최종 확정 결과·PDF URL(송신)
+          <t>마케팅허브에서 광고 시안·동영상 심의 의뢰를 수신하고, AI 사전 판정 대조 뷰어 링크 제공 및 RA 최종 확정 결과를 회신합니다.
+[입력] 마케팅허브 심의신청 페이로드(수신), AI 판정 뷰어 딥링크 및 RA 최종 확정 결과·PDF URL(송신)
 [처리로직]
-1. 티움넷 심의 의뢰 웹훅/API 수신 시 심의요청 자동 생성 및 시안 파일 연동
-2. 티움넷 내 결과 확인 클릭 시 SSO 연동된 Side-by-Side 대조 뷰어 화면 제공
-3. RA 최종 승인/반려 확정 시 판정 결과 요약 및 리포트 PDF 링크를 티움넷으로 즉시 송신
-[출력] 티움넷 연동 트랜잭션 결과 및 ACK 로그</t>
+1. 마케팅허브 심의 의뢰 웹훅/API 수신 시 심의요청 자동 생성 및 시안 파일 연동
+2. 마케팅허브 내 결과 확인 클릭 시 SSO 연동된 Side-by-Side 대조 뷰어 화면 제공
+3. RA 최종 승인/반려 확정 시 판정 결과 요약 및 리포트 PDF 링크를 마케팅허브으로 즉시 송신
+[출력] 마케팅허브 연동 트랜잭션 결과 및 ACK 로그</t>
         </is>
       </c>
       <c r="J40" s="142" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="B41" s="143" t="inlineStr">
         <is>
-          <t>마이비커(ProductLab) 실증·전성분 연계 및 [Option] KT 레몬 연동</t>
+          <t>프로덕트랩(ProductLab) 실증·전성분 연계 및 [Option] KT 레몬 연동</t>
         </is>
       </c>
       <c r="C41" s="142" t="inlineStr">

--- a/public/templates/office/EMP_DEG_020_기능정의서.xlsx
+++ b/public/templates/office/EMP_DEG_020_기능정의서.xlsx
@@ -2416,7 +2416,7 @@
       </c>
       <c r="C12" s="170" t="inlineStr">
         <is>
-          <t>한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
       <c r="D12" s="121" t="n"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="D4" s="176" t="inlineStr">
         <is>
-          <t>착수보고서(v1.8) 및 킥오프 합의(동영상 사용자 지정 장면 캡처, 마케팅허브/프로덕트랩 연계, KT레몬 Option, AWS EC2) 반영</t>
+          <t>착수보고서(v1.8) 및 킥오프 합의(CAD/PDF 설계도면 규격영역 스냅샷 추출, 전자구매포털/피엘엠넥서스 연계, HB-Monitor Option, AWS EC2) 반영</t>
         </is>
       </c>
       <c r="E4" s="175" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="F4" s="177" t="inlineStr">
         <is>
-          <t>한빛글로벌 RA</t>
+          <t>한빛글로벌 QA</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="D5" s="25" t="inlineStr">
         <is>
-          <t>5대 모듈(통합웹 Client/fe · 업무서버 be · 대외API api · AI Agent · Batch) 구성, 영상 피크프레임·미세각주 자동 추출, 과거 상충 탐지, 실증요청 메일, Naver/Paddle OCR 선택, 동시 4건 대기열(QUEUED), PG Vector 1536d 반영</t>
+          <t>5대 모듈(통합웹 Client/fe · 업무서버 be · 대외API api · AI Agent · Batch) 구성, 도면 핵심규격·특약주석 자동 추출, 과거 상충 탐지, 성적서요청 메일, Enterprise Vision OCR 선택, 동시 4건 대기열(QUEUED), PG Vector 1536d 반영</t>
         </is>
       </c>
       <c r="E5" s="26" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>1차 AI Agent OpenCV 영상 피크프레임 자동 추출 및 2차 통합 웹 화면 동영상 재생·특정화면 멈춤 장면 추가/편집/삭제 보정(BO➔Agent EKS Service 호출), S3 업로드 시 'Intelligent-Tiering' 자동 적용, BO/대외연계 ALB 물리 분리 반영</t>
+          <t>1차 AI Agent OpenCV 영상 도면스냅샷 자동 추출 및 2차 통합 웹 화면 설계도면 재생·특정화면 멈춤 장면 추가/편집/삭제 보정(BO➔Agent EKS Service 호출), S3 업로드 시 'Intelligent-Tiering' 자동 적용, BO/대외연계 ALB 물리 분리 반영</t>
         </is>
       </c>
       <c r="E6" s="26" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="B5" s="143" t="inlineStr">
         <is>
-          <t>문서 및 동영상 장면 파싱</t>
+          <t>문서 및 설계도면 장면 파싱</t>
         </is>
       </c>
       <c r="C5" s="142" t="inlineStr">
@@ -2984,24 +2984,24 @@
       </c>
       <c r="I5" s="143" t="inlineStr">
         <is>
-          <t>PPTX, PDF, 긴 상세페이지(JPG) 및 동영상(MP4, 최대 300MB 대외 연계 API 직접 업로드)에서 1차로 AI Agent가 OpenCV를 통해 텍스트 애니메이션 완성 시점(피크프레임)과 하단 미세 각주를 자동 추출하고, 2차로 이를 보정하기 위해 웹 화면(:3104)에서 동영상을 재생하여 사용자가 특정 화면에 멈춰 장면을 추가하거나 AI가 만든 장면을 편집·삭제합니다.
-[입력] PPTX, PDF, 긴 JPG, MP4 동영상(최대 300MB) 및 웹 화면 사용자 보정 장면
+          <t>PPTX, PDF, 다단 기술시방서(PDF/TIFF) 및 설계도면(CAD/PDF, 최대 300MB 대외 연계 API 직접 업로드)에서 1차로 AI Agent가 OpenCV를 통해 텍스트 애니메이션 완성 시점(도면스냅샷)과 하단 미세 특약주석를 자동 추출하고, 2차로 이를 보정하기 위해 웹 화면(:3104)에서 설계도면을 재생하여 사용자가 특정 화면에 멈춰 장면을 추가하거나 AI가 만든 장면을 편집·삭제합니다.
+[입력] PPTX, PDF, 긴 JPG, CAD/PDF 설계도면(최대 300MB) 및 웹 화면 사용자 보정 장면
 [처리로직]
-1. 대용량 파일(300MB): 대외 연계 전용 ALB(마케팅허브만 오픈) 및 BO 전용 ALB(사용자대역 오픈)를 통해 S3(Intelligent-Tiering 자동 적용) 업로드
-2. 동영상 1차 자동 추출: AI Agent(:18083)가 OpenCV 기반으로 영상 피크프레임 및 하단 미세 각주 장면을 1차 자동 추출하여 S3에 저장
-3. 동영상 2차 웹 보정: 통합 웹 화면(:3104)에서 동영상을 재생하고 사용자가 특정 화면에 멈춰 장면을 추가하거나 AI가 생성한 장면을 편집·삭제하면, BO 서버(:18080)가 EKS Service로 AI Agent(:18083)를 호출하여 재분석 수행
-[출력] 슬라이드/피크프레임·보정 장면별 구조화 JSON 및 이미지 스냅샷 메타데이터</t>
+1. 대용량 파일(300MB): 대외 연계 전용 ALB(전자구매포털만 오픈) 및 BO 전용 ALB(사용자대역 오픈)를 통해 S3(Intelligent-Tiering 자동 적용) 업로드
+2. 설계도면 1차 자동 추출: AI Agent(:18083)가 OpenCV 기반으로 영상 도면스냅샷 및 하단 미세 특약주석 장면을 1차 자동 추출하여 S3에 저장
+3. 설계도면 2차 웹 보정: 통합 웹 화면(:3104)에서 설계도면을 재생하고 사용자가 특정 화면에 멈춰 장면을 추가하거나 AI가 생성한 장면을 편집·삭제하면, BO 서버(:18080)가 EKS Service로 AI Agent(:18083)를 호출하여 재분석 수행
+[출력] 슬라이드/도면스냅샷·보정 장면별 구조화 JSON 및 이미지 스냅샷 메타데이터</t>
         </is>
       </c>
       <c r="J5" s="142" t="inlineStr">
         <is>
-          <t>PPTX, PDF, 긴 상세페이지(JPG) 및 동영상(MP4, 최대 300MB 대외 연계 API 직접 업로드)에서 1차로 AI Agent가 OpenCV를 통해 텍스트 애니메이션 완성 시점(피크프레임)과 하단 미세 각주를 자동 추출하고, 2차로 이를 보정하기 위해 웹 화면(:3104)에서 동영상을 재생하여 사용자가 특정 화면에 멈춰 장면을 추가하거나 AI가 만든 장면을 편집·삭제합니다.
-[입력] PPTX, PDF, 긴 JPG, MP4 동영상(최대 300MB) 및 웹 화면 사용자 보정 장면
+          <t>PPTX, PDF, 다단 기술시방서(PDF/TIFF) 및 설계도면(CAD/PDF, 최대 300MB 대외 연계 API 직접 업로드)에서 1차로 AI Agent가 OpenCV를 통해 텍스트 애니메이션 완성 시점(도면스냅샷)과 하단 미세 특약주석를 자동 추출하고, 2차로 이를 보정하기 위해 웹 화면(:3104)에서 설계도면을 재생하여 사용자가 특정 화면에 멈춰 장면을 추가하거나 AI가 만든 장면을 편집·삭제합니다.
+[입력] PPTX, PDF, 긴 JPG, CAD/PDF 설계도면(최대 300MB) 및 웹 화면 사용자 보정 장면
 [처리로직]
-1. 대용량 파일(300MB): 대외 연계 전용 ALB(마케팅허브만 오픈) 및 BO 전용 ALB(사용자대역 오픈)를 통해 S3(Intelligent-Tiering 자동 적용) 업로드
-2. 동영상 1차 자동 추출: AI Agent(:18083)가 OpenCV 기반으로 영상 피크프레임 및 하단 미세 각주 장면을 1차 자동 추출하여 S3에 저장
-3. 동영상 2차 웹 보정: 통합 웹 화면(:3104)에서 동영상을 재생하고 사용자가 특정 화면에 멈춰 장면을 추가하거나 AI가 생성한 장면을 편집·삭제하면, BO 서버(:18080)가 EKS Service로 AI Agent(:18083)를 호출하여 재분석 수행
-[출력] 슬라이드/피크프레임·보정 장면별 구조화 JSON 및 이미지 스냅샷 메타데이터</t>
+1. 대용량 파일(300MB): 대외 연계 전용 ALB(전자구매포털만 오픈) 및 BO 전용 ALB(사용자대역 오픈)를 통해 S3(Intelligent-Tiering 자동 적용) 업로드
+2. 설계도면 1차 자동 추출: AI Agent(:18083)가 OpenCV 기반으로 영상 도면스냅샷 및 하단 미세 특약주석 장면을 1차 자동 추출하여 S3에 저장
+3. 설계도면 2차 웹 보정: 통합 웹 화면(:3104)에서 설계도면을 재생하고 사용자가 특정 화면에 멈춰 장면을 추가하거나 AI가 생성한 장면을 편집·삭제하면, BO 서버(:18080)가 EKS Service로 AI Agent(:18083)를 호출하여 재분석 수행
+[출력] 슬라이드/도면스냅샷·보정 장면별 구조화 JSON 및 이미지 스냅샷 메타데이터</t>
         </is>
       </c>
       <c r="K5" s="144" t="inlineStr">
@@ -3060,21 +3060,21 @@
       </c>
       <c r="I6" s="143" t="inlineStr">
         <is>
-          <t>시안 내 이미지, 긴 상세페이지(JPG/PNG), 스캔본 PDF 및 동영상 사용자 지정 캡처 스냅샷 이미지에서 국문/영문 혼용 텍스트를 추출합니다.
-[입력] 시안 래스터 이미지 및 동영상 캡처 스냅샷 이미지
+          <t>계약·도서 내 이미지, 다단 기술시방서(PDF/TIFF), 스캔본 PDF 및 설계도면 사용자 지정 스냅샷 스냅샷 이미지에서 국문/영문 혼용 텍스트를 추출합니다.
+[입력] 계약·도서 래스터 이미지 및 동도면 스냅샷 스냅샷 이미지
 [처리로직]
 1. 이미지 전처리 (해상도 정규화, 기울기·대비 보정)
 2. Vision OCR을 통한 텍스트 및 바운딩 박스 상대좌표(%) 추출
-3. 국·영문 혼용 문구 번역 연계 및 저신뢰 구간 수동 교정 플래그 부여
+3. 국·영문 혼용 조항 번역 연계 및 저신뢰 구간 수동 교정 플래그 부여
 [출력] 문장별 추출 텍스트, 신뢰도 점수, 바운딩 박스 좌표</t>
         </is>
       </c>
       <c r="J6" s="142" t="inlineStr">
         <is>
-          <t>시안 내 이미지, 긴 상세페이지(JPG/PNG), 스캔본 PDF 및 동영상 사용자 지정 캡처 스냅샷 이미지에서 설정(claim.ocr.provider)에 따라 네이버 클로바 OCR 또는 패들 OCR을 선택 구동하여 국/영문 텍스트를 추출합니다.
-[입력] 시안 래스터 이미지 및 동영상 캡처 스냅샷 이미지
+          <t>계약·도서 내 이미지, 다단 기술시방서(PDF/TIFF), 스캔본 PDF 및 설계도면 사용자 지정 스냅샷 스냅샷 이미지에서 설정(Spec.ocr.provider)에 따라 엔터프라이즈 비전 OCR 또는 도면 OCR을 선택 구동하여 국/영문 텍스트를 추출합니다.
+[입력] 계약·도서 래스터 이미지 및 동도면 스냅샷 스냅샷 이미지
 [처리로직]
-1. 설정 기반 OCR 엔진 선택: claim.ocr.provider 설정값(NAVER | PADDLE | AUTO)에 따라 네이버 클로바 OCR 또는 자체 구축 패들 OCR(PaddleOCR) 실행
+1. 설정 기반 OCR 엔진 선택: Spec.ocr.provider 설정값(NAVER | PADDLE | AUTO)에 따라 엔터프라이즈 비전 OCR 또는 자체 구축 도면 OCR(PaddleOCR) 실행
 2. AUTO 모드 시 주 엔진 장애 발생 시 보조 엔진으로 자동 폴백(Fallback) 처리
 3. 바운딩 박스 상대좌표(%) 추출 및 저신뢰 구간 수동 교정 플래그 부여
 [출력] 문장별 추출 텍스트, 신뢰도 점수, 바운딩 박스 좌표, 사용 OCR 엔진 식별자</t>
@@ -3136,14 +3136,14 @@
       </c>
       <c r="I7" s="143" t="inlineStr">
         <is>
-          <t>추출된 원문 텍스트를 심의 가능한 개별 광고 문구 문장 단위로 분리하고 각주 및 메타정보를 결합합니다.
+          <t>추출된 원문 텍스트를 검증 가능한 개별 구매계약 조항 문장 단위로 분리하고 특약주석 및 메타정보를 결합합니다.
 [입력] 파싱 텍스트 및 OCR 추출 텍스트.
 [처리로직]
 1. 한국어 문장 분리기(KSS/정규식)를 적용하여 종결 어미, 줄바꿈, 특수기호 기반 분리.
-2. 주석 기호(`*`, `※`, `†`, `1)`)와 하단 각주(Footnote) 텍스트를 탐색하여 해당 문장과 양방향 링크 매핑.
-3. 브랜드명, 법인명, 전성분 단순 나열, 바코드 번호 등 비검토 대상 텍스트 자동 필터링 및 분류.
+2. 주석 기호(`*`, `※`, `†`, `1)`)와 하단 특약주석(Footnote) 텍스트를 탐색하여 해당 문장과 양방향 링크 매핑.
+3. 사업본부명, 법인명, 자재BOM 단순 나열, 바코드 번호 등 비검토 대상 텍스트 자동 필터링 및 분류.
 4. 동일 슬라이드 내 중복 문장 병합 및 슬라이드-문장 위치 좌표 매핑.
-[출력] 슬라이드 번호, 문장 고유키, 원문 텍스트, 연결 각주, 바운딩 박스 정보를 가진 문장 엔티티 리스트.</t>
+[출력] 슬라이드 번호, 문장 고유키, 원문 텍스트, 연결 특약주석, 바운딩 박스 정보를 가진 문장 엔티티 리스트.</t>
         </is>
       </c>
       <c r="J7" s="145" t="inlineStr">
@@ -3207,8 +3207,8 @@
       </c>
       <c r="I8" s="143" t="inlineStr">
         <is>
-          <t>식약처 제품 표시·광고 관리 지침, 질의응답집, 서울식약청 위반 사례집 등 규제 문서를 체계적으로 적재합니다.
-[입력] PDF, HWP, DOCX 형태의 식약처 및 공정위 공식 가이드라인 문서.
+          <t>공정위·표준원 구매계약·기술규격 관리 지침, 질의응답집, 서울식약청 위반 사례집 등 규제 문서를 체계적으로 적재합니다.
+[입력] PDF, HWP, DOCX 형태의 공정위 및 산업부 공식 가이드라인 문서.
 [처리로직]
 1. HWP/PDF 문서 파싱 및 조항(제N조, 별표, [사례]) 단위 의미론적 청킹(Semantic Chunking).
 2. 메타데이터 태깅 (문서명, 소관부처, 제정/개정일자, 관련 법 조항 번호, 규제 분류 코드).
@@ -3277,14 +3277,14 @@
       </c>
       <c r="I9" s="143" t="inlineStr">
         <is>
-          <t>식약처 지침 및 과거 위반 사례를 바탕으로 표현 사전을 구축하고 자동/수동 승인 파이프라인을 운영합니다.
-[입력] 규제 문서, 과거 심의 이력 DB, RA 검수 데이터.
+          <t>공정위·표준원 지침 및 과거 위반 사례를 바탕으로 표현 사전을 구축하고 자동/수동 승인 파이프라인을 운영합니다.
+[입력] 규제 문서, 과거 검증 이력 DB, QA 검수 데이터.
 [처리로직]
 1. LLM 보조를 활용하여 규제 텍스트에서 금지/주의 표현 키워드 및 패턴 자동 1차 추출.
 2. 등급(금지: PROHIBITED, 주의: CAUTION, 조건부허용: CONDITIONAL, 허용: ALLOWED) 부여.
 3. 5대 카테고리 태깅 및 근거 법률 조항 매핑.
-4. RA 전문가의 웹 UI 검수 및 최종 승인 시 룰 엔진 반영.
-[출력] 승인된 표현 사전 마스터 테이블 (`review_rule_dict`).</t>
+4. 법무·QA 전문위원의 웹 UI 검수 및 최종 승인 시 룰 엔진 반영.
+[출력] 승인된 표현 사전 마스터 테이블 (`verify_rule_dict`).</t>
         </is>
       </c>
       <c r="J9" s="142" t="inlineStr">
@@ -3349,7 +3349,7 @@
       <c r="I10" s="143" t="inlineStr">
         <is>
           <t>신규 및 수정된 규제 청크와 과거 판정 사례를 고차원 벡터 및 역색인 키워드로 변환하여 적재합니다.
-[입력] 규제 조항 청크, 표현 사전 항목, 과거 확정 심의 문장.
+[입력] 규제 조항 청크, 표현 사전 항목, 과거 확정 검증 문장.
 [처리로직]
 1. 최신 다국어 텍스트 임베딩 모델을 활용하여 1536/1024차원 Dense Vector 생성.
 2. PostgreSQL `pgvector` 또는 벡터 인덱스(HNSW/IVFFlat)에 적재.
@@ -3361,7 +3361,7 @@
       <c r="J10" s="145" t="inlineStr">
         <is>
           <t>신규 및 수정된 규제 청크와 과거 판정 사례를 PostgreSQL pgvector 1536차원(VECTOR(1536)) 단일 벡터 인덱스 및 역색인 키워드로 변환하여 적재합니다.
-[입력] 규제 조항 청크, 표현 사전 항목, 과거 확정 심의 문장.
+[입력] 규제 조항 청크, 표현 사전 항목, 과거 확정 검증 문장.
 [처리로직]
 1. 1536차원 임베딩 모델을 활용하여 Dense Vector(VECTOR(1536)) 생성 후 PostgreSQL pgvector HNSW 인덱스에 단일화 적재
 2. GIN Trigram 형태소 역색인 키워드 결합 하이브리드 검색 지원
@@ -3425,13 +3425,13 @@
       </c>
       <c r="I11" s="143" t="inlineStr">
         <is>
-          <t>심의 대상 문장과 의미론적/키워드적으로 가장 관련 있는 규제 조항 및 유사 판정 사례를 고속 검색합니다.
-[입력] 심의 대상 단일 문장, 제품 카테고리(기능성/일반), 대상 국가(KR).
+          <t>검증 대상 문장과 의미론적/키워드적으로 가장 관련 있는 규제 조항 및 유사 판정 사례를 고속 검색합니다.
+[입력] 검증 대상 단일 문장, 제품 카테고리(핵심규격/일반), 대상 국가(KR).
 [처리로직]
 1. Dense Vector 유사도 검색 (Cosine Similarity Top-K).
 2. Sparse Keyword 검색 (BM25 / TF-IDF Top-K).
 3. RRF(Reciprocal Rank Fusion) 알고리즘으로 점수 결합 및 Re-ranking.
-4. 식약처 공식 조항, 한빛글로벌 과거 내부 심의 이력, 경쟁사 위반 사례 동시 검색.
+4. 공정위·표준원 공식 조항, 한빛글로벌 과거 내부 검증 이력, 경쟁사 위반 사례 동시 검색.
 [출력] 유사도 점수와 출처 메타정보가 포함된 상위 3~5개 근거 청크.</t>
         </is>
       </c>
@@ -3497,7 +3497,7 @@
       <c r="I12" s="143" t="inlineStr">
         <is>
           <t>검색된 규제 조항을 바탕으로 AI가 판단 근거를 구조화하여 생성하고 환각을 원천 검증합니다.
-[입력] 심의 문장, 검색된 근거 청크, 룰 매칭 결과.
+[입력] 검증 문장, 검색된 근거 청크, 룰 매칭 결과.
 [처리로직]
 1. 근거 유형(법령 조항, 가이드라인 세부기준, 과거 위반사례, 내부 커미티 결정)별 구조화.
 2. LLM 출력 근거가 검색된 원문 컨텍스트에 실제로 존재하는지 토큰 단위 Exact/Fuzzy 매칭 검증(Citation Verification).
@@ -3566,14 +3566,14 @@
       </c>
       <c r="I13" s="143" t="inlineStr">
         <is>
-          <t>과거 심의 완료된 이력 DB에서 동일 또는 유사 문장의 최종 RA 판정을 검색하여 일관성을 보장합니다.
-[입력] 심의 문장 임베딩 및 정규화 키.
+          <t>과거 검증 완료된 이력 DB에서 동일 또는 유사 문장의 최종 법무·QA 판정을 검색하여 일관성을 보장합니다.
+[입력] 검증 문장 임베딩 및 정규화 키.
 [처리로직]
 1. 문장 정규화 키(특수문자/공백 제거 해시)로 완전 일치 문장 탐색.
 2. 벡터 코사인 유사도 95% 이상 문장 탐색.
-3. 과거 판정(승인/반려/수정) 내역 및 확정 Claim을 프롬프트 Few-shot 컨텍스트에 최우선 주입.
+3. 과거 판정(승인/반려/수정) 내역 및 확정 Spec을 프롬프트 Few-shot 컨텍스트에 최우선 주입.
 4. UI 상에 "과거 동일/유사 판정 사례 존재" 배지 표시.
-[출력] 과거 심의 일자, 당시 판정 등급, 확정 Claim, 심의자 코멘트.</t>
+[출력] 과거 검증 일자, 당시 판정 등급, 확정 Spec, 검증자 코멘트.</t>
         </is>
       </c>
       <c r="J13" s="145" t="inlineStr">
@@ -3638,7 +3638,7 @@
       <c r="I14" s="143" t="inlineStr">
         <is>
           <t>표현 사전 및 정규식 패턴을 기반으로 1차 즉각 매칭을 수행하여 카테고리를 부여합니다.
-[입력] 심의 문장.
+[입력] 검증 문장.
 [처리로직]
 1. Aho-Corasick 알고리즘 및 Regex 패턴 매칭으로 고속 검사.
 2. 5대 카테고리 매핑:
@@ -3714,7 +3714,7 @@
 2. **No-Downgrade 핵심 규칙**: 룰 엔진에서 `금지(PROHIBITED)`로 매칭된 경우, LLM이 문맥상 안전하다고 보더라도 최종 등급을 `주의` 또는 `안전`으로 하향할 수 없음 (보수적 규제 안전성 확보).
 3. 등급(SAFE, CAUTION, PROHIBITED), 상세 사유, 신뢰도 점수(0.0~1.0) 산출.
 4. 프롬프트 버전 및 사용 모델 메타 기록.
-[출력] `SyncGuardAnalysis` JSON 결과.</t>
+[출력] `SyncFlowAnalysis` JSON 결과.</t>
         </is>
       </c>
       <c r="J15" s="142" t="inlineStr">
@@ -3778,14 +3778,14 @@
       </c>
       <c r="I16" s="143" t="inlineStr">
         <is>
-          <t>주의/금지 판정을 받은 문장에 대해 규제를 준수하면서 마케팅 소구를 유지하는 대체 표현을 2~3개 제안합니다.
+          <t>주의/금지 판정을 받은 문장에 대해 규제를 준수하면서 구매조달 기술사양를 유지하는 대체 표현을 2~3개 제안합니다.
 [입력] 문제 문장, 위반 카테고리, 근거 조항, 제품 특성.
 [처리로직]
-1. 승인 표현 DB(`review_rule_dict` 중 ALLOWED)에서 매칭되는 표준 표현 우선 검색 및 추천.
-2. 부족분은 LLM을 통해 뉘앙스별(예: 효능 강조형, 안전 표현형, 감성 소구형) 2~3개 생성.
+1. 승인 표현 DB(`verify_rule_dict` 중 ALLOWED)에서 매칭되는 표준 표현 우선 검색 및 추천.
+2. 부족분은 LLM을 통해 뉘앙스별(예: 성능규격 강조형, 안전 표현형, 감성 기술사양형) 2~3개 생성.
 3. 생성된 대체 표현을 룰 엔진에 재입력하여 위반 여부 자동 검증 (재금지 시 자동 재생성).
-4. 제안별 준수 사유 및 마케팅 뉘앙스 설명 생성.
-[출력] 권장 대체 문구 리스트 (문구 텍스트, 설명, 신뢰도).</t>
+4. 제안별 준수 사유 및 구매조달 뉘앙스 설명 생성.
+[출력] 권장 대체 조항 리스트 (조항 텍스트, 설명, 신뢰도).</t>
         </is>
       </c>
       <c r="J16" s="142" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="B17" s="143" t="inlineStr">
         <is>
-          <t>실증자료 필요 여부 판단</t>
+          <t>시험성적서 필요 여부 판단</t>
         </is>
       </c>
       <c r="C17" s="142" t="inlineStr">
@@ -3849,13 +3849,13 @@
       </c>
       <c r="I17" s="143" t="inlineStr">
         <is>
-          <t>문장 내 효능·효과 소구 표현에 대해 법적 실증자료(시험성적서/임상결과)가 필요한지 분류합니다.
-[입력] 심의 문장, 판정 등급.
+          <t>문장 내 성능·규격 기술사양 표현에 대해 법적 시험성적서(시험성적서/신뢰성결과)가 필요한지 분류합니다.
+[입력] 검증 문장, 판정 등급.
 [처리로직]
-1. 소구 유형 분류: 수치 표현(예: 99.9% 개선), 임상 효능(예: 모공 수 축소), 기능성 인증, 비교 우위.
-2. 필요 실증 유형 도출:
-3. 불확실하거나 모호한 경우 '실증자료 필요(REQUIRED)'로 보수적 판정.
-[출력] 실증 필요 여부(REQUIRED / NOT_REQUIRED), 권장 실증 유형, 실증 가이드 메모.</t>
+1. 기술사양 유형 분류: 수치 표현(예: 99.9% 개선), 신뢰성 성능규격(예: 불량률 PPM 감축), 핵심규격 인증, 비교 우위.
+2. 필요 시험검증 유형 도출:
+3. 불확실하거나 모호한 경우 '시험성적서 필요(REQUIRED)'로 보수적 판정.
+[출력] 시험검증 필요 여부(REQUIRED / NOT_REQUIRED), 권장 시험검증 유형, 시험검증 가이드 메모.</t>
         </is>
       </c>
       <c r="J17" s="145" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="I18" s="143" t="inlineStr">
         <is>
-          <t>판정, 대체문구 생성, 실증 분석, 동영상 캡처 장면 문맥 분석 등 단계별 프롬프트 템플릿의 버전, 파라미터, 변수를 관리합니다.
+          <t>판정, 표준수정조항 생성, 시험검증 분석, 설계도면 도면 스냅샷 문맥 분석 등 단계별 프롬프트 템플릿의 버전, 파라미터, 변수를 관리합니다.
 [입력] 단계별 시스템/유저 프롬프트 템플릿, 모델 라우팅 설정, 하이퍼파라미터(Temperature, Top-P)
 [처리로직]
 1. 프롬프트 템플릿 버전 이력 저장 및 변경 전·후 Diff 비교
@@ -3989,10 +3989,10 @@
       </c>
       <c r="I19" s="143" t="inlineStr">
         <is>
-          <t>LLM 응답의 정합성 검증, 필수 금지어 강제 차단(No-Downgrade), 타임아웃/폴백 및 토큰 비용 로깅을 전담합니다.
+          <t>LLM 응답의 정합성 검증, 필수 독소조항 강제 차단(No-Downgrade), 타임아웃/폴백 및 토큰 비용 로깅을 전담합니다.
 [입력] 1단계 룰 매칭 결과, 2단계 RAG 검색 청크, 3단계 LLM 판정 응답 JSON
 [처리로직]
-1. 1단계 확정 금지어 매칭 문장은 LLM이 임의로 '안전'으로 하향 판정하지 못하도록 No-Downgrade 규칙 강제 적용
+1. 1단계 확정 독소조항 매칭 문장은 LLM이 임의로 '안전'으로 하향 판정하지 못하도록 No-Downgrade 규칙 강제 적용
 2. JSON 출력 스키마 유효성 검증 및 인용 법령 조항의 실제 RAG 존재 여부 교차 검증(환각 차단)
 3. 외부 API 응답 지연 시 재시도 및 폴백 처리, 요청별 토큰 사용량 기록
 [출력] 무결성이 검증된 최종 3단계 판정 결과 및 비용/지연시간 감사 로그</t>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="B20" s="143" t="inlineStr">
         <is>
-          <t>SyncGuard AI 1차 검토 자동 파이프라인</t>
+          <t>SyncFlow AI 1차 검토 자동 파이프라인</t>
         </is>
       </c>
       <c r="C20" s="142" t="inlineStr">
@@ -4059,12 +4059,12 @@
       </c>
       <c r="I20" s="143" t="inlineStr">
         <is>
-          <t>마케팅허브/포털 시안 및 동영상 캡처 장면 등록 시 파싱부터 집계까지 비동기 작업 파이프라인을 총괄 오케스트레이션합니다.
-[입력] 심의요청 ID, 시안 파일 및 동영상 캡처 스냅샷 목록, 제품/처방 코드
+          <t>전자구매포털/포털 계약·도서 및 설계도면 도면 스냅샷 등록 시 파싱부터 집계까지 비동기 작업 파이프라인을 총괄 오케스트레이션합니다.
+[입력] 검증요청 ID, 계약·도서 파일 및 동도면 스냅샷 스냅샷 목록, 제품/설계사양 코드
 [처리로직]
-1. 파이프라인 단계: 시안/스냅샷 수신 ➔ 파싱·OCR(F-01/02) ➔ 문장 분리(F-03) ➔ 전성분 RDB·표현사전 룰 매칭(F-10) ➔ 법령·ProductLab 실증 RAG(F-07) ➔ 비학습 LLM 3단계 판정 및 대체문구 생성(F-11/12)
+1. 파이프라인 단계: 계약·도서/스냅샷 수신 ➔ 파싱·OCR(F-01/02) ➔ 문장 분리(F-03) ➔ 자재BOM RDB·표현사전 룰 매칭(F-10) ➔ 법령·PLM-Nexus 시험검증 RAG(F-07) ➔ 비학습 LLM 3단계 판정 및 표준수정조항 생성(F-11/12)
 2. 장애 대응: AWS EC2 AI Worker 및 Redis 큐 기반 비동기 분산 처리, 실패 문장 최대 3회 재시도, 진행률(0~100%) 실시간 갱신
-[출력] 문장/장면별 1차 AI 심의 결과 세트 및 종합 위험도 요약</t>
+[출력] 문장/장면별 1차 AI 검증 결과 세트 및 종합 위험도 요약</t>
         </is>
       </c>
       <c r="J20" s="142" t="inlineStr">
@@ -4128,10 +4128,10 @@
       </c>
       <c r="I21" s="143" t="inlineStr">
         <is>
-          <t>마케터(본인/팀 시안 등록), 연구원(실증 검증), RA(최종 심의/승인), 관리자(전체 통제) 권한 격리.
+          <t>구매담당자(본인/팀 계약·도서 등록), 연구원(시험검증 검증), QA(최종 검증/승인), 관리자(전체 통제) 권한 격리.
 [입력] 시스템 및 사용자 입력 파라미터
 [처리로직]
-마케터(본인/팀 시안 등록), 연구원(실증 검증), RA(최종 심의/승인), 관리자(전체 통제) 권한 격리.
+구매담당자(본인/팀 계약·도서 등록), 연구원(시험검증 검증), QA(최종 검증/승인), 관리자(전체 통제) 권한 격리.
 [출력] 처리 결과 및 DB 반영</t>
         </is>
       </c>
@@ -4196,10 +4196,10 @@
       </c>
       <c r="I22" s="143" t="inlineStr">
         <is>
-          <t>AI 1차 검토 완료, 실증자료 제출 요청, RA 배정/심의 완료 시 인앱 알림 및 이메일 전송.
+          <t>AI 1차 검토 완료, 시험성적서 제출 요청, QA 배정/검증 완료 시 인앱 알림 및 이메일 전송.
 [입력] 시스템 및 사용자 입력 파라미터
 [처리로직]
-AI 1차 검토 완료, 실증자료 제출 요청, RA 배정/심의 완료 시 인앱 알림 및 이메일 전송.
+AI 1차 검토 완료, 시험성적서 제출 요청, QA 배정/검증 완료 시 인앱 알림 및 이메일 전송.
 [출력] 처리 결과 및 DB 반영</t>
         </is>
       </c>
@@ -4264,12 +4264,12 @@
       </c>
       <c r="I23" s="143" t="inlineStr">
         <is>
-          <t>AWS S3 기반 PPTX/PDF/긴 JPG 및 동영상(MP4)·AI 추출 피크프레임·사용자 보정 장면 업로드, 'Intelligent-Tiering' 스토리지 클래스 자동 적용, Pre-signed URL 발급 및 해시 무결성 검증을 수행합니다.
-[입력] 업로드 원본 파일, AI 피크프레임 및 웹 사용자 보정 장면 이미지 스트림
+          <t>AWS S3 기반 PPTX/PDF/긴 JPG 및 설계도면(CAD/PDF)·AI 추출 도면스냅샷·사용자 보정 장면 업로드, 'Intelligent-Tiering' 스토리지 클래스 자동 적용, Pre-signed URL 발급 및 해시 무결성 검증을 수행합니다.
+[입력] 업로드 원본 파일, AI 도면스냅샷 및 웹 사용자 보정 장면 이미지 스트림
 [처리로직]
 1. S3 업로드 시 파일 저장 타입으로 'Intelligent-Tiering'(x-amz-storage-class: INTELLIGENT_TIERING)을 자동 적용하여, 파일 보관주기 미확정에 따른 접근 패턴 자동 분석 및 스토리지 보관비용 최적화
 2. AWS S3 버킷 멀티파트 업로드 및 서버 측 암호화(SSE-S3 / AES-256) 적용
-3. 파일 및 캡처 장면별 SHA-256 무결성 해시 산출 및 보안 열람용 Pre-signed URL 발급
+3. 파일 및 도면 스냅샷별 SHA-256 무결성 해시 산출 및 보안 열람용 Pre-signed URL 발급
 [출력] S3 오브젝트 키(Intelligent-Tiering 적용), Pre-signed URL, SHA-256 해시값</t>
         </is>
       </c>
@@ -4334,10 +4334,10 @@
       </c>
       <c r="I24" s="143" t="inlineStr">
         <is>
-          <t>브랜드/제품/국가/매체/유형(사전검수, 정식의뢰) 선택, 파일 드래그앤드롭 업로드, 채번(`REQ-YYYYMMDD-XXXX`).
+          <t>사업본부/제품/국가/매체/유형(사전검수, 정식의뢰) 선택, 파일 드래그앤드롭 업로드, 채번(`REQ-YYYYMMDD-XXXX`).
 [입력] 시스템 및 사용자 입력 파라미터
 [처리로직]
-브랜드/제품/국가/매체/유형(사전검수, 정식의뢰) 선택, 파일 드래그앤드롭 업로드, 채번(`REQ-YYYYMMDD-XXXX`).
+사업본부/제품/국가/매체/유형(사전검수, 정식의뢰) 선택, 파일 드래그앤드롭 업로드, 채번(`REQ-YYYYMMDD-XXXX`).
 [출력] 처리 결과 및 DB 반영</t>
         </is>
       </c>
@@ -4402,10 +4402,10 @@
       </c>
       <c r="I25" s="143" t="inlineStr">
         <is>
-          <t>상태별(접수, AI검토중, RA검토중, 완료), 위험도별 필터링 및 페이징 목록.
+          <t>상태별(접수, AI검토중, QA검토중, 완료), 위험도별 필터링 및 페이징 목록.
 [입력] 시스템 및 사용자 입력 파라미터
 [처리로직]
-상태별(접수, AI검토중, RA검토중, 완료), 위험도별 필터링 및 페이징 목록.
+상태별(접수, AI검토중, QA검토중, 완료), 위험도별 필터링 및 페이징 목록.
 [출력] 처리 결과 및 DB 반영</t>
         </is>
       </c>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="B26" s="143" t="inlineStr">
         <is>
-          <t>실증자료 요청 안내 (메일 발송)</t>
+          <t>시험성적서 요청 안내 (메일 발송)</t>
         </is>
       </c>
       <c r="C26" s="142" t="inlineStr">
@@ -4470,10 +4470,10 @@
       </c>
       <c r="I26" s="143" t="inlineStr">
         <is>
-          <t>실증 필요 문장 발생 시 담당 연구원에게 전용 웹 링크와 함께 제출 요청 메일 발송.
+          <t>시험검증 필요 문장 발생 시 담당 연구원에게 전용 웹 링크와 함께 제출 요청 메일 발송.
 [입력] 시스템 및 사용자 입력 파라미터
 [처리로직]
-실증 필요 문장 발생 시 담당 연구원에게 전용 웹 링크와 함께 제출 요청 메일 발송.
+시험검증 필요 문장 발생 시 담당 연구원에게 전용 웹 링크와 함께 제출 요청 메일 발송.
 [출력] 처리 결과 및 DB 반영</t>
         </is>
       </c>
@@ -4538,10 +4538,10 @@
       </c>
       <c r="I27" s="143" t="inlineStr">
         <is>
-          <t>문장별 판정, 근거 법령, 대체 표현, 실증 매핑 정보를 포함한 공식 심의 리포트 다운로드.
+          <t>문장별 판정, 근거 법령, 대체 표현, 시험검증 매핑 정보를 포함한 공식 검증 리포트 다운로드.
 [입력] 시스템 및 사용자 입력 파라미터
 [처리로직]
-문장별 판정, 근거 법령, 대체 표현, 실증 매핑 정보를 포함한 공식 심의 리포트 다운로드.
+문장별 판정, 근거 법령, 대체 표현, 시험검증 매핑 정보를 포함한 공식 검증 리포트 다운로드.
 [출력] 처리 결과 및 DB 반영</t>
         </is>
       </c>
@@ -4606,10 +4606,10 @@
       </c>
       <c r="I28" s="143" t="inlineStr">
         <is>
-          <t>RA 심의 확정 시 요청자 및 유관부서에 리포트 다운로드 링크와 함께 최종 결과 자동 통보.
+          <t>QA 검증 확정 시 요청자 및 유관부서에 리포트 다운로드 링크와 함께 최종 결과 자동 통보.
 [입력] 시스템 및 사용자 입력 파라미터
 [처리로직]
-RA 심의 확정 시 요청자 및 유관부서에 리포트 다운로드 링크와 함께 최종 결과 자동 통보.
+QA 검증 확정 시 요청자 및 유관부서에 리포트 다운로드 링크와 함께 최종 결과 자동 통보.
 [출력] 처리 결과 및 DB 반영</t>
         </is>
       </c>
@@ -4674,10 +4674,10 @@
       </c>
       <c r="I29" s="143" t="inlineStr">
         <is>
-          <t>상단 로고, 글로벌 네비게이션(검토요청, 검토결과, 심의이력, 실증검증, 관리자), 사용자 역할 배지, 대외비 표기.
+          <t>상단 로고, 글로벌 네비게이션(검토요청, 검토결과, 검증이력, 시험검증검증, 관리자), 사용자 역할 배지, 대외비 표기.
 [입력] 시스템 및 사용자 입력 파라미터
 [처리로직]
-상단 로고, 글로벌 네비게이션(검토요청, 검토결과, 심의이력, 실증검증, 관리자), 사용자 역할 배지, 대외비 표기.
+상단 로고, 글로벌 네비게이션(검토요청, 검토결과, 검증이력, 시험검증검증, 관리자), 사용자 역할 배지, 대외비 표기.
 [출력] 처리 결과 및 DB 반영</t>
         </is>
       </c>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="B30" s="143" t="inlineStr">
         <is>
-          <t>검토 대상 문장 및 동영상 캡처 장면 편집기</t>
+          <t>검토 대상 문장 및 설계도면 도면 스냅샷 편집기</t>
         </is>
       </c>
       <c r="C30" s="142" t="inlineStr">
@@ -4742,13 +4742,13 @@
       </c>
       <c r="I30" s="143" t="inlineStr">
         <is>
-          <t>AI Agent가 OpenCV로 1차 자동 추출한 영상 피크프레임 결과를 확인하고, 이를 보정하기 위해 웹 화면(:3104)에서 동영상을 재생하여 사용자가 특정 화면에 멈춰 장면을 추가하거나 AI가 만든 장면을 편집·삭제한 뒤 BO 서버(:18080)에서 AI Agent(:18083)를 호출합니다.
-[입력] 원본 시안/동영상 스트림, AI 1차 추출 피크프레임 목록, 사용자 추가·편집·삭제 보정 장면
+          <t>AI Agent가 OpenCV로 1차 자동 추출한 영상 도면스냅샷 결과를 확인하고, 이를 보정하기 위해 웹 화면(:3104)에서 설계도면을 재생하여 사용자가 특정 화면에 멈춰 장면을 추가하거나 AI가 만든 장면을 편집·삭제한 뒤 BO 서버(:18080)에서 AI Agent(:18083)를 호출합니다.
+[입력] 원본 계약·도서/설계도면 스트림, AI 1차 추출 도면스냅샷 목록, 사용자 추가·편집·삭제 보정 장면
 [처리로직]
-1. AI 1차 추출 장면 로드 후 통합 웹 플레이어에서 동영상 재생 및 특정 화면 일시정지 시점의 장면(스크린샷) 수동 추가
-2. AI가 자동 생성한 피크프레임 장면의 텍스트·구간 편집 또는 불필요 장면 삭제 보정
-3. 장면 보정 완료 시 BO 업무 서버(:18080)에서 EKS K8s Service를 통해 AI Agent(:18083)로 재분석·심의 호출
-[출력] 보정 완료된 심의 대상 장면 이미지(S3 Intelligent-Tiering 저장) 및 정제 문장 리스트</t>
+1. AI 1차 추출 장면 로드 후 통합 웹 플레이어에서 설계도면 재생 및 특정 화면 일시정지 시점의 장면(스크린샷) 수동 추가
+2. AI가 자동 생성한 도면스냅샷 장면의 텍스트·구간 편집 또는 불필요 장면 삭제 보정
+3. 장면 보정 완료 시 BO 업무 서버(:18080)에서 EKS K8s Service를 통해 AI Agent(:18083)로 재분석·검증 호출
+[출력] 보정 완료된 검증 대상 장면 이미지(S3 Intelligent-Tiering 저장) 및 정제 문장 리스트</t>
         </is>
       </c>
       <c r="J30" s="142" t="inlineStr">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="B31" s="143" t="inlineStr">
         <is>
-          <t>실증 검증 화면</t>
+          <t>시험검증 검증 화면</t>
         </is>
       </c>
       <c r="C31" s="142" t="inlineStr">
@@ -4812,10 +4812,10 @@
       </c>
       <c r="I31" s="143" t="inlineStr">
         <is>
-          <t>AI가 실증 필요로 분류한 문장에 대해 연구원이 '확인완료/불필요' 판정하고 시험성적서 링크 및 페이지 메모 등록.
+          <t>AI가 시험검증 필요로 분류한 문장에 대해 연구원이 '확인완료/불필요' 판정하고 시험성적서 링크 및 페이지 메모 등록.
 [입력] 시스템 및 사용자 입력 파라미터
 [처리로직]
-AI가 실증 필요로 분류한 문장에 대해 연구원이 '확인완료/불필요' 판정하고 시험성적서 링크 및 페이지 메모 등록.
+AI가 시험검증 필요로 분류한 문장에 대해 연구원이 '확인완료/불필요' 판정하고 시험성적서 링크 및 페이지 메모 등록.
 [출력] 처리 결과 및 DB 반영</t>
         </is>
       </c>
@@ -4913,7 +4913,7 @@
       </c>
       <c r="B33" s="143" t="inlineStr">
         <is>
-          <t>RA 최종 판정 입력 (피드백 UI)</t>
+          <t>QA 최종 판정 입력 (피드백 UI)</t>
         </is>
       </c>
       <c r="C33" s="142" t="inlineStr">
@@ -4948,10 +4948,10 @@
       </c>
       <c r="I33" s="143" t="inlineStr">
         <is>
-          <t>RA 담당자가 AI 판정 승인/수정, 대체 표현 채택/직접 작성, 확정 Claim 입력, 일괄 승인 및 완료 처리.
+          <t>법무·QA 담당자가 AI 판정 승인/수정, 대체 표현 채택/직접 작성, 확정 Spec 입력, 일괄 승인 및 완료 처리.
 [입력] 시스템 및 사용자 입력 파라미터
 [처리로직]
-RA 담당자가 AI 판정 승인/수정, 대체 표현 채택/직접 작성, 확정 Claim 입력, 일괄 승인 및 완료 처리.
+법무·QA 담당자가 AI 판정 승인/수정, 대체 표현 채택/직접 작성, 확정 Spec 입력, 일괄 승인 및 완료 처리.
 [출력] 처리 결과 및 DB 반영</t>
         </is>
       </c>
@@ -5016,10 +5016,10 @@
       </c>
       <c r="I34" s="143" t="inlineStr">
         <is>
-          <t>표현 키워드, 제품, 브랜드, 기간, 판정 등급 및 시맨틱 유사 표현 검색, 과거 심의 타임라인 조회.
+          <t>표현 키워드, 제품, 사업본부, 기간, 판정 등급 및 시맨틱 유사 표현 검색, 과거 검증 타임라인 조회.
 [입력] 시스템 및 사용자 입력 파라미터
 [처리로직]
-표현 키워드, 제품, 브랜드, 기간, 판정 등급 및 시맨틱 유사 표현 검색, 과거 심의 타임라인 조회.
+표현 키워드, 제품, 사업본부, 기간, 판정 등급 및 시맨틱 유사 표현 검색, 과거 검증 타임라인 조회.
 [출력] 처리 결과 및 DB 반영</t>
         </is>
       </c>
@@ -5084,10 +5084,10 @@
       </c>
       <c r="I35" s="143" t="inlineStr">
         <is>
-          <t>골든셋 대상 일괄 검토 실행, 정확도(Accuracy), 정밀도(Precision), 재현율(Recall), RA 일치율 자동 산출 및 버전 간 비교.
+          <t>골든셋 대상 일괄 검토 실행, 정확도(Accuracy), 정밀도(Precision), 재현율(Recall), QA 일치율 자동 산출 및 버전 간 비교.
 [입력] 시스템 및 사용자 입력 파라미터
 [처리로직]
-골든셋 대상 일괄 검토 실행, 정확도(Accuracy), 정밀도(Precision), 재현율(Recall), RA 일치율 자동 산출 및 버전 간 비교.
+골든셋 대상 일괄 검토 실행, 정확도(Accuracy), 정밀도(Precision), 재현율(Recall), QA 일치율 자동 산출 및 버전 간 비교.
 [출력] 처리 결과 및 DB 반영</t>
         </is>
       </c>
@@ -5152,10 +5152,10 @@
       </c>
       <c r="I36" s="143" t="inlineStr">
         <is>
-          <t>RA 확정 시 원문, AI 판정, RA 최종 판정, 실증 링크, 심의자 메타를 불변 테이블에 영구 보존.
+          <t>QA 확정 시 원문, AI 판정, QA 최종 판정, 시험검증 링크, 검증자 메타를 불변 테이블에 영구 보존.
 [입력] 시스템 및 사용자 입력 파라미터
 [처리로직]
-RA 확정 시 원문, AI 판정, RA 최종 판정, 실증 링크, 심의자 메타를 불변 테이블에 영구 보존.
+QA 확정 시 원문, AI 판정, QA 최종 판정, 시험검증 링크, 검증자 메타를 불변 테이블에 영구 보존.
 [출력] 처리 결과 및 DB 반영</t>
         </is>
       </c>
@@ -5220,10 +5220,10 @@
       </c>
       <c r="I37" s="143" t="inlineStr">
         <is>
-          <t>RA가 승인한 표현 및 확정 Claim을 표현 사전에 자동 등록하고 프롬프트 Few-shot 예시 풀에 반영.
+          <t>QA가 승인한 표현 및 확정 Spec을 표현 사전에 자동 등록하고 프롬프트 Few-shot 예시 풀에 반영.
 [입력] 시스템 및 사용자 입력 파라미터
 [처리로직]
-RA가 승인한 표현 및 확정 Claim을 표현 사전에 자동 등록하고 프롬프트 Few-shot 예시 풀에 반영.
+QA가 승인한 표현 및 확정 Spec을 표현 사전에 자동 등록하고 프롬프트 Few-shot 예시 풀에 반영.
 [출력] 처리 결과 및 DB 반영</t>
         </is>
       </c>
@@ -5288,10 +5288,10 @@
       </c>
       <c r="I38" s="143" t="inlineStr">
         <is>
-          <t>대표적인 과거 심의 사례 및 엣지 케이스를 카테고리별로 균형 있게 선별하여 표준 평가셋(Golden Set) 버전 관리.
+          <t>대표적인 과거 검증 사례 및 엣지 케이스를 카테고리별로 균형 있게 선별하여 표준 평가셋(Golden Set) 버전 관리.
 [입력] 시스템 및 사용자 입력 파라미터
 [처리로직]
-대표적인 과거 심의 사례 및 엣지 케이스를 카테고리별로 균형 있게 선별하여 표준 평가셋(Golden Set) 버전 관리.
+대표적인 과거 검증 사례 및 엣지 케이스를 카테고리별로 균형 있게 선별하여 표준 평가셋(Golden Set) 버전 관리.
 [출력] 처리 결과 및 DB 반영</t>
         </is>
       </c>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="B40" s="143" t="inlineStr">
         <is>
-          <t>마케팅허브(MarketingHub) 양방향 API 연동</t>
+          <t>전자구매포털(SRM-Portal) 양방향 API 연동</t>
         </is>
       </c>
       <c r="C40" s="142" t="inlineStr">
@@ -5424,13 +5424,13 @@
       </c>
       <c r="I40" s="143" t="inlineStr">
         <is>
-          <t>마케팅허브에서 광고 시안·동영상 심의 의뢰를 수신하고, AI 사전 판정 대조 뷰어 링크 제공 및 RA 최종 확정 결과를 회신합니다.
-[입력] 마케팅허브 심의신청 페이로드(수신), AI 판정 뷰어 딥링크 및 RA 최종 확정 결과·PDF URL(송신)
+          <t>전자구매포털에서 구매계약 계약·도서·설계도면 검증 요청를 수신하고, AI 사전 판정 대조 뷰어 링크 제공 및 QA 최종 확정 결과를 회신합니다.
+[입력] 전자구매포털 검증신청 페이로드(수신), AI 판정 뷰어 딥링크 및 QA 최종 확정 결과·PDF URL(송신)
 [처리로직]
-1. 마케팅허브 심의 의뢰 웹훅/API 수신 시 심의요청 자동 생성 및 시안 파일 연동
-2. 마케팅허브 내 결과 확인 클릭 시 SSO 연동된 Side-by-Side 대조 뷰어 화면 제공
-3. RA 최종 승인/반려 확정 시 판정 결과 요약 및 리포트 PDF 링크를 마케팅허브으로 즉시 송신
-[출력] 마케팅허브 연동 트랜잭션 결과 및 ACK 로그</t>
+1. 전자구매포털 검증 요청 웹훅/API 수신 시 검증요청 자동 생성 및 계약·도서 파일 연동
+2. 전자구매포털 내 결과 확인 클릭 시 SSO 연동된 Side-by-Side 대조 뷰어 화면 제공
+3. QA 최종 승인/반려 확정 시 판정 결과 요약 및 리포트 PDF 링크를 전자구매포털으로 즉시 송신
+[출력] 전자구매포털 연동 트랜잭션 결과 및 ACK 로그</t>
         </is>
       </c>
       <c r="J40" s="142" t="inlineStr">
@@ -5459,7 +5459,7 @@
       </c>
       <c r="B41" s="143" t="inlineStr">
         <is>
-          <t>프로덕트랩(ProductLab) 실증·전성분 연계 및 [Option] KT 레몬 연동</t>
+          <t>피엘엠넥서스(PLM-Nexus) 시험검증·자재BOM 연계 및 [Option] HB-Monitor 연동</t>
         </is>
       </c>
       <c r="C41" s="142" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="I41" s="143" t="inlineStr">
         <is>
-          <t>ProductLab 및 사내 전성분 RDB를 통해 제품 전성분·배합한도·인체적용시험 실증자료를 연동하며, [Option] KT 레몬 API는 비교 검증 후 연계합니다.
-[입력] 제품/처방 코드, 소구 문장 키워드, [Option] 연구보고서 검색 질의
+          <t>PLM-Nexus 및 사내 자재BOM RDB를 통해 제품 자재BOM·유해물질한도·공인신뢰성시험 시험성적서를 연동하며, [Option] HB-Monitor API는 비교 검증 후 연계합니다.
+[입력] 제품/설계사양 코드, 기술사양 조항 키워드, [Option] 연구보고서 검색 질의
 [처리로직]
-1. [필수] 사내 전성분 RDB 및 ProductLab API를 호출하여 원료 배합한도 준수 여부 및 인체적용시험·세포효능 실증보고서 매핑
-2. [Option] KT 레몬 연구보고서 벡터 검색 API와 상용 LLM 직접 파싱 방식의 정확도 비교 PoC 결과에 따라 플러그인 연동
-[출력] 전성분 규격 검증 결과, 매핑된 실증 시험성적서 메타데이터</t>
+1. [필수] 사내 자재BOM RDB 및 PLM-Nexus API를 호출하여 원소재 유해물질한도 준수 여부 및 공인신뢰성시험·배상한도성능규격 시험검증보고서 매핑
+2. [Option] HB-Monitor 연구보고서 벡터 검색 API와 상용 LLM 직접 파싱 방식의 정확도 비교 PoC 결과에 따라 플러그인 연동
+[출력] 자재BOM 규격 검증 결과, 매핑된 시험검증 시험성적서 메타데이터</t>
         </is>
       </c>
       <c r="J41" s="142" t="inlineStr">
@@ -5563,10 +5563,10 @@
       </c>
       <c r="I42" s="143" t="inlineStr">
         <is>
-          <t>SSO 사용자 목록 동기화, 브랜드/부서 배정, 역할 부여, 계정 비활성화, 권한 변경 감사 로그.
+          <t>SSO 사용자 목록 동기화, 사업본부/부서 배정, 역할 부여, 계정 비활성화, 권한 변경 감사 로그.
 [입력] 시스템 및 사용자 입력 파라미터
 [처리로직]
-SSO 사용자 목록 동기화, 브랜드/부서 배정, 역할 부여, 계정 비활성화, 권한 변경 감사 로그.
+SSO 사용자 목록 동기화, 사업본부/부서 배정, 역할 부여, 계정 비활성화, 권한 변경 감사 로그.
 [출력] 처리 결과 및 DB 반영</t>
         </is>
       </c>
@@ -5631,10 +5631,10 @@
       </c>
       <c r="I43" s="143" t="inlineStr">
         <is>
-          <t>식약처 가이드라인 등록/개정/폐기, 청킹 미리보기, RAG 임베딩 재인덱싱 트리거 및 진행률 모니터링.
+          <t>공정위·표준원 가이드라인 등록/개정/폐기, 청킹 미리보기, RAG 임베딩 재인덱싱 트리거 및 진행률 모니터링.
 [입력] 시스템 및 사용자 입력 파라미터
 [처리로직]
-식약처 가이드라인 등록/개정/폐기, 청킹 미리보기, RAG 임베딩 재인덱싱 트리거 및 진행률 모니터링.
+공정위·표준원 가이드라인 등록/개정/폐기, 청킹 미리보기, RAG 임베딩 재인덱싱 트리거 및 진행률 모니터링.
 [출력] 처리 결과 및 DB 반영</t>
         </is>
       </c>
@@ -5835,10 +5835,10 @@
       </c>
       <c r="I46" s="143" t="inlineStr">
         <is>
-          <t>기간별 검토 건수, 위험 등급 분포 차트, AI-RA 일치율 추이, LLM 토큰 사용량 및 비용 분석.
+          <t>기간별 검토 건수, 위험 등급 분포 차트, AI-QA 일치율 추이, LLM 토큰 사용량 및 비용 분석.
 [입력] 시스템 및 사용자 입력 파라미터
 [처리로직]
-기간별 검토 건수, 위험 등급 분포 차트, AI-RA 일치율 추이, LLM 토큰 사용량 및 비용 분석.
+기간별 검토 건수, 위험 등급 분포 차트, AI-QA 일치율 추이, LLM 토큰 사용량 및 비용 분석.
 [출력] 처리 결과 및 DB 반영</t>
         </is>
       </c>
@@ -5903,10 +5903,10 @@
       </c>
       <c r="I47" s="143" t="inlineStr">
         <is>
-          <t>브랜드, 제품 카테고리, 광고 매체, 실증 유형, 심의 카테고리 코드 관리 및 사용 중 코드 삭제 방지.
+          <t>사업본부, 제품 카테고리, 구매계약 매체, 시험검증 유형, 검증 카테고리 코드 관리 및 사용 중 코드 삭제 방지.
 [입력] 시스템 및 사용자 입력 파라미터
 [처리로직]
-브랜드, 제품 카테고리, 광고 매체, 실증 유형, 심의 카테고리 코드 관리 및 사용 중 코드 삭제 방지.
+사업본부, 제품 카테고리, 구매계약 매체, 시험검증 유형, 검증 카테고리 코드 관리 및 사용 중 코드 삭제 방지.
 [출력] 처리 결과 및 DB 반영</t>
         </is>
       </c>
